--- a/NV_DEMO/Assets/StreamingAssets/Story/1.xlsx
+++ b/NV_DEMO/Assets/StreamingAssets/Story/1.xlsx
@@ -11,12 +11,6 @@
     <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
     <sheet name="Sheet3" sheetId="3" r:id="rId3"/>
   </sheets>
-  <definedNames>
-    <definedName name="人物名称">Sheet1!$A:$A</definedName>
-    <definedName name="台词">Sheet1!$B:$B</definedName>
-    <definedName name="人物头像">Sheet1!$C:$C</definedName>
-    <definedName name="人物音频">Sheet1!$D:$D</definedName>
-  </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
@@ -35,12 +29,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="87" uniqueCount="37">
-  <si>
-    <t>Name</t>
-  </si>
-  <si>
-    <t>Dialogue</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="31" uniqueCount="24">
+  <si>
+    <t>中文姓名</t>
+  </si>
+  <si>
+    <t>中文对话</t>
   </si>
   <si>
     <t>Avatar</t>
@@ -49,103 +43,70 @@
     <t>Vocal</t>
   </si>
   <si>
-    <t>Bgimage</t>
+    <t>BgImg</t>
   </si>
   <si>
     <t>Bgm</t>
   </si>
   <si>
-    <t>Character1Action</t>
-  </si>
-  <si>
-    <t>x1</t>
-  </si>
-  <si>
-    <t>Character1img</t>
-  </si>
-  <si>
-    <t>Character2Action</t>
-  </si>
-  <si>
-    <t>x2</t>
-  </si>
-  <si>
-    <t>Character2img</t>
-  </si>
-  <si>
-    <t>...</t>
-  </si>
-  <si>
-    <t>nightcity_rooftop</t>
-  </si>
-  <si>
-    <t>.....</t>
+    <t>Action1</t>
+  </si>
+  <si>
+    <t>X1</t>
+  </si>
+  <si>
+    <t>Character1</t>
+  </si>
+  <si>
+    <t>Action2</t>
+  </si>
+  <si>
+    <t>X2</t>
+  </si>
+  <si>
+    <t>Character2</t>
+  </si>
+  <si>
+    <t>安妮</t>
+  </si>
+  <si>
+    <t>一</t>
   </si>
   <si>
     <t>Annie</t>
   </si>
   <si>
-    <t>这是哪？</t>
-  </si>
-  <si>
     <t>appearAt</t>
   </si>
   <si>
-    <t>奇怪，怎么一点也想不起来了...</t>
-  </si>
-  <si>
     <t>[Name]</t>
   </si>
   <si>
-    <t>诶呀!</t>
+    <t>二</t>
   </si>
   <si>
     <t>Bella</t>
   </si>
   <si>
-    <t>moveTo</t>
-  </si>
-  <si>
-    <t>谁在那里!</t>
-  </si>
-  <si>
-    <t>...被发现了</t>
-  </si>
-  <si>
-    <t>我知道你现在有很多的疑惑</t>
-  </si>
-  <si>
-    <t>...我可以帮你找回遗失的记忆</t>
-  </si>
-  <si>
-    <t>你可以吗?[Name]</t>
-  </si>
-  <si>
-    <t>应该可以...跟我走</t>
-  </si>
-  <si>
-    <t>disappear</t>
-  </si>
-  <si>
-    <t>抓紧跟上吧...</t>
-  </si>
-  <si>
-    <t>她跟上了没...</t>
-  </si>
-  <si>
-    <t>呀！</t>
-  </si>
-  <si>
-    <t>吓到你了?</t>
+    <t>三</t>
+  </si>
+  <si>
+    <t>四</t>
   </si>
   <si>
     <t>choice</t>
   </si>
   <si>
-    <t>去我家</t>
-  </si>
-  <si>
-    <t>去你家</t>
+    <t>甲
+乙
+丙
+丁</t>
+  </si>
+  <si>
+    <t>1-1-1
+1-1-2
+1-1-3
+1-1-4</t>
   </si>
 </sst>
 </file>
@@ -616,157 +577,163 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="43" fontId="0" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="0" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="0" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="3">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="4">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="5">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="4">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="6">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="7">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="8">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="6" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="7" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="8" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="9" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="10" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="11" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="12" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="13" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="14" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="15" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="16" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="17" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="18" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="19" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="20" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="21" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="22" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="23" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="24" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="25" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="26" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="27" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="28" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="29" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="30" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="31" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="32" borderId="0">
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="4">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="49">
@@ -1079,351 +1046,149 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:N17"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
+  <dimension ref="A1:P6"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="5"/>
   <cols>
-    <col min="1" max="1" width="9" style="1"/>
-    <col min="2" max="2" width="11.875" style="1" customWidth="1"/>
-    <col min="3" max="5" width="9" style="1"/>
-    <col min="6" max="6" width="4.375" style="1" customWidth="1"/>
-    <col min="7" max="7" width="17.75" style="1" customWidth="1"/>
-    <col min="8" max="8" width="4.375" style="1" customWidth="1"/>
-    <col min="9" max="9" width="14.875" style="1" customWidth="1"/>
-    <col min="10" max="10" width="17.625" style="1" customWidth="1"/>
-    <col min="11" max="11" width="7.5" style="1" customWidth="1"/>
-    <col min="12" max="12" width="14.75" style="1" customWidth="1"/>
-    <col min="13" max="13" width="10.875" customWidth="1"/>
-    <col min="14" max="14" width="10.75" customWidth="1"/>
-    <col min="15" max="16" width="9" style="1"/>
+    <col min="1" max="2" width="14.0916666666667" customWidth="1"/>
+    <col min="3" max="3" width="7.59166666666667" customWidth="1"/>
+    <col min="4" max="5" width="8.59166666666667" customWidth="1"/>
+    <col min="6" max="6" width="4.59166666666667" customWidth="1"/>
+    <col min="7" max="7" width="10.6833333333333" customWidth="1"/>
+    <col min="8" max="8" width="5.59166666666667" customWidth="1"/>
+    <col min="9" max="9" width="11.8166666666667" customWidth="1"/>
+    <col min="10" max="10" width="10.6833333333333" customWidth="1"/>
+    <col min="11" max="11" width="5.59166666666667" customWidth="1"/>
+    <col min="12" max="12" width="11.8166666666667" customWidth="1"/>
+    <col min="13" max="13" width="14.0916666666667" customWidth="1"/>
+    <col min="14" max="14" width="18.5916666666667" style="1" customWidth="1"/>
+    <col min="15" max="15" width="11.8166666666667" customWidth="1"/>
+    <col min="16" max="16" width="20.8166666666667" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14">
-      <c r="A1" s="1" t="s">
+    <row r="1" spans="1:16">
+      <c r="A1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="F1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="G1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="H1" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="I1" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="J1" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="1" t="s">
+      <c r="K1" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="1" t="s">
+      <c r="L1" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="1"/>
-      <c r="N1" s="1"/>
     </row>
-    <row r="2" spans="1:14">
+    <row r="2" spans="1:16">
+      <c r="A2" t="s">
+        <v>12</v>
+      </c>
       <c r="B2" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="C2" t="s">
+        <v>14</v>
+      </c>
+      <c r="E2">
+        <v>1</v>
+      </c>
+      <c r="G2" t="s">
+        <v>15</v>
+      </c>
+      <c r="H2">
+        <v>0</v>
+      </c>
+      <c r="I2" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="3" spans="1:16">
+      <c r="A3" t="s">
+        <v>16</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="C3" t="s">
+        <v>18</v>
+      </c>
+      <c r="E3">
+        <v>2</v>
+      </c>
+      <c r="J3" t="s">
+        <v>15</v>
+      </c>
+      <c r="K3">
+        <v>0</v>
+      </c>
+      <c r="L3" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="4" spans="1:16">
+      <c r="A4" t="s">
         <v>12</v>
       </c>
-      <c r="E2" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="F2" s="1">
-        <v>1</v>
+      <c r="B4" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="C4" t="s">
+        <v>14</v>
+      </c>
+      <c r="E4">
+        <v>3</v>
       </c>
     </row>
-    <row r="3" spans="1:14">
-      <c r="B3" s="1" t="s">
-        <v>14</v>
+    <row r="5" spans="1:16">
+      <c r="A5" t="s">
+        <v>16</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C5" t="s">
+        <v>18</v>
+      </c>
+      <c r="E5">
+        <v>4</v>
       </c>
     </row>
-    <row r="4" spans="1:14">
-      <c r="A4" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="B4" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="C4" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="G4" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="H4" s="1">
-        <v>0</v>
-      </c>
-      <c r="I4" s="1" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="5" spans="1:14">
-      <c r="A5" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="B5" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="C5" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="I5" s="1" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="6" spans="1:14">
-      <c r="A6" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="B6" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="C6" s="1" t="s">
+    <row r="6" ht="54" spans="1:16">
+      <c r="A6" t="s">
         <v>21</v>
       </c>
-      <c r="G6" s="1" t="s">
+      <c r="B6" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="H6" s="1">
-        <v>0</v>
-      </c>
-      <c r="I6" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="J6" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="K6" s="1">
-        <v>0</v>
-      </c>
-      <c r="L6" s="1" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="7" spans="1:14">
-      <c r="A7" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="B7" s="1" t="s">
+      <c r="C6" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="C7" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="I7" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="L7" s="1" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="8" spans="1:14">
-      <c r="A8" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="B8" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="C8" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="I8" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="L8" s="1" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="9" spans="1:14">
-      <c r="A9" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="B9" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="C9" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="I9" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="L9" s="1" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="10" spans="1:14">
-      <c r="A10" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="B10" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="C10" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="I10" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="L10" s="1" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="11" spans="1:14">
-      <c r="A11" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="B11" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="C11" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="G11" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="H11" s="1">
-        <v>400</v>
-      </c>
-      <c r="I11" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="L11" s="1" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="12" spans="1:14">
-      <c r="A12" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="B12" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="C12" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="I12" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="J12" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="K12" s="1"/>
-      <c r="L12" s="1" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="13" spans="1:14">
-      <c r="A13" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="B13" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="C13" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="G13" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="I13" s="1" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="14" spans="1:14">
-      <c r="A14" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="B14" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="C14" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="E14" s="1">
-        <v>2</v>
-      </c>
-      <c r="J14" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="K14" s="1">
-        <v>0</v>
-      </c>
-      <c r="L14" s="1" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="15" spans="1:14">
-      <c r="A15" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="B15" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="C15" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="G15" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="H15" s="1">
-        <v>0</v>
-      </c>
-      <c r="I15" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="L15" s="1" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="16" spans="1:14">
-      <c r="A16" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="B16" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="C16" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="I16" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="L16" s="1" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5">
-      <c r="A17" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="B17" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="C17" s="1">
-        <v>2</v>
-      </c>
-      <c r="D17" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="E17" s="1">
-        <v>3</v>
-      </c>
+      <c r="N6" s="3"/>
+      <c r="P6" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
